--- a/costos_baterias.xlsx
+++ b/costos_baterias.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ce3gk\OneDrive\Escritorio\opti\proyecto\ics1113_proyecto_grupo03\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marti\OneDrive\Documentos\UC\Semester 6\OPTI\tarea\Proyecto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{710FAD86-CE8E-4DD1-90C7-9DC3C3696A3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DA728B8-95F4-445A-8002-7A58D3CFA0A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="c" sheetId="1" r:id="rId1"/>
-    <sheet name="c01" sheetId="2" r:id="rId2"/>
+    <sheet name="c_chico" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -43,37 +43,19 @@
   <commentList>
     <comment ref="A2" authorId="0" shapeId="0" xr:uid="{C1F9F7C4-9990-4B4A-AB15-ED69A81EEB95}">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Aptos Narrow"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t>[Comentario encadenado]
+Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Comentario:
     Ion-litio</t>
-        </r>
       </text>
     </comment>
     <comment ref="A3" authorId="1" shapeId="0" xr:uid="{861A2C9A-BD86-454A-A22C-D1B1F17181B4}">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Aptos Narrow"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t xml:space="preserve">[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t xml:space="preserve">[Comentario encadenado]
+Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Comentario:
     Redox_flow
 </t>
-        </r>
       </text>
     </comment>
   </commentList>
@@ -83,43 +65,25 @@
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
-    <author>tc={C1F9F7C4-9990-4B4A-AB15-ED69A81EEB95}</author>
-    <author>tc={861A2C9A-BD86-454A-A22C-D1B1F17181B4}</author>
+    <author>tc={C1F9F7C4-9990-4B4B-AB15-ED69A81EEB95}</author>
+    <author>tc={861A2C9A-BD86-454B-A22C-D1B1F17181B4}</author>
   </authors>
   <commentList>
     <comment ref="A2" authorId="0" shapeId="0" xr:uid="{D95D0FA1-ED81-4133-9A4F-4EB874B09644}">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Aptos Narrow"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t>[Comentario encadenado]
+Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Comentario:
     Ion-litio</t>
-        </r>
       </text>
     </comment>
     <comment ref="A3" authorId="1" shapeId="0" xr:uid="{AB94AD79-35C4-4E00-AE33-A9C2D604E0D6}">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Aptos Narrow"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t xml:space="preserve">[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t xml:space="preserve">[Comentario encadenado]
+Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Comentario:
     Redox_flow
 </t>
-        </r>
       </text>
     </comment>
   </commentList>
@@ -520,16 +484,28 @@
 </ThreadedComments>
 </file>
 
+<file path=xl/threadedComments/threadedComment2.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="A2" dT="2025-10-27T01:35:09.92" personId="{4C2204B3-03F6-478C-A773-D4EEF5967187}" id="{C1F9F7C4-9990-4B4B-AB15-ED69A81EEB95}">
+    <text>Ion-litio</text>
+  </threadedComment>
+  <threadedComment ref="A3" dT="2025-10-27T01:33:35.51" personId="{4C2204B3-03F6-478C-A773-D4EEF5967187}" id="{861A2C9A-BD86-454B-A22C-D1B1F17181B4}">
+    <text xml:space="preserve">Redox_flow
+</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.88671875" customWidth="1"/>
-    <col min="2" max="2" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.90625" customWidth="1"/>
+    <col min="2" max="2" width="11.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -537,7 +513,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -545,7 +521,7 @@
         <v>662400</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
@@ -562,9 +538,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B97AE0F-56B5-4482-A7FB-9EAA6D9D3898}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -572,20 +548,20 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2">
-        <v>6000</v>
+        <v>192000</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3">
-        <v>14000</v>
+        <v>1440000</v>
       </c>
     </row>
   </sheetData>
